--- a/data_lake/macro/Europe/PMI.xlsx
+++ b/data_lake/macro/Europe/PMI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0976A3-E1E6-4B6D-9E4F-9F1E73D64FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5DF86F-B5B2-4EC5-88B0-6798FFCDA220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DF312ACE-5C57-4A44-B252-1A5D09CC9E56}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF312ACE-5C57-4A44-B252-1A5D09CC9E56}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
@@ -11876,7 +11876,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D2" s="2" t="str">
-        <f t="shared" ref="D2:D65" si="0">IF(
+        <f>IF(
  AND(
   B2 &gt;= EOMONTH(DATE(YEAR(B2),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B2),3,1),0),1)
@@ -11910,7 +11910,20 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D2:D65" si="0">IF(
+ AND(
+  B3 &gt;= EOMONTH(DATE(YEAR(B3),3,1),0)
+        - WEEKDAY(EOMONTH(DATE(YEAR(B3),3,1),0),1)
+        + 1
+        + TIME(2,0,0),
+  B3 &lt; EOMONTH(DATE(YEAR(B3),10,1),0)
+       - WEEKDAY(EOMONTH(DATE(YEAR(B3),10,1),0),1)
+       + 1
+       + TIME(3,0,0)
+ ),
+ "UTC+2",
+ "UTC+1"
+)</f>
         <v>UTC+2</v>
       </c>
       <c r="E3" s="1">
